--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/Panel-28/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.28699</v>
+        <v>16.82656</v>
       </c>
       <c r="D2" t="n">
-        <v>16.33452</v>
+        <v>16.59376</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53807</v>
+        <v>16.75008</v>
       </c>
       <c r="F2" t="n">
-        <v>42.00829</v>
+        <v>42.70446</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05048</v>
+        <v>0.05033</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78882</v>
+        <v>1.7944</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61476</v>
+        <v>16.85729</v>
       </c>
       <c r="D3" t="n">
-        <v>16.41796</v>
+        <v>16.4606</v>
       </c>
       <c r="E3" t="n">
-        <v>16.9282</v>
+        <v>16.66364</v>
       </c>
       <c r="F3" t="n">
-        <v>41.63522</v>
+        <v>42.82463</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05076</v>
+        <v>0.04997</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8098</v>
+        <v>1.78566</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.50279</v>
+        <v>16.5337</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60279</v>
+        <v>16.4221</v>
       </c>
       <c r="E4" t="n">
-        <v>16.44362</v>
+        <v>16.44486</v>
       </c>
       <c r="F4" t="n">
-        <v>41.54846</v>
+        <v>41.82945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05022</v>
+        <v>0.04975</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80844</v>
+        <v>1.77871</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8601</v>
+        <v>16.23738</v>
       </c>
       <c r="D6" t="n">
-        <v>16.09466</v>
+        <v>15.73692</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41956</v>
+        <v>16.18888</v>
       </c>
       <c r="F6" t="n">
-        <v>21.87386</v>
+        <v>21.50424</v>
       </c>
       <c r="G6" t="n">
-        <v>34.06561</v>
+        <v>34.12604</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.68819</v>
+        <v>16.39753</v>
       </c>
       <c r="D7" t="n">
-        <v>16.32823</v>
+        <v>15.81405</v>
       </c>
       <c r="E7" t="n">
-        <v>16.6549</v>
+        <v>16.21774</v>
       </c>
       <c r="F7" t="n">
-        <v>21.08683</v>
+        <v>22.05796</v>
       </c>
       <c r="G7" t="n">
-        <v>34.67486</v>
+        <v>33.50644</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.66713</v>
+        <v>16.74994</v>
       </c>
       <c r="D8" t="n">
-        <v>15.88023</v>
+        <v>15.88602</v>
       </c>
       <c r="E8" t="n">
-        <v>16.52861</v>
+        <v>16.10513</v>
       </c>
       <c r="F8" t="n">
-        <v>21.86717</v>
+        <v>21.76585</v>
       </c>
       <c r="G8" t="n">
-        <v>33.65362</v>
+        <v>33.6845</v>
       </c>
     </row>
   </sheetData>
